--- a/out/LSTM-mamba2_repeat_3_000007.xlsx
+++ b/out/LSTM-mamba2_repeat_3_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.901262215535431</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001907775237525348</v>
+        <v>-7.712256331345998e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.199383012872231</v>
+        <v>0.889109252280405</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
-        <v>4.402166026517913</v>
+        <v>1.779592907008404</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3298073164246632</v>
+        <v>0.1333258984963202</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.859445620448554</v>
+        <v>1.155942144807108</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4123664578916351</v>
+        <v>0.1667007545622656</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.354423595509047</v>
+        <v>1.356038928517799</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.5911251991053647</v>
+        <v>0.2389645784281521</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.124540578076084</v>
+        <v>1.667361733030028</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.6323872211502458</v>
+        <v>0.2556451129256772</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC44" t="n">
-        <v>4.798233569177909</v>
+        <v>1.939704871897068</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.6702029908713697</v>
+        <v>0.2709315542955592</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>5.506300182504891</v>
+        <v>2.225943688836998</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3024494789631552</v>
+        <v>0.1222670373213373</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>5.440440546272648</v>
+        <v>2.19931958941948</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1460699175820781</v>
+        <v>0.05904874746033055</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>5.42989240798476</v>
+        <v>2.19505546025556</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.06959796694958495</v>
+        <v>0.02813558306727647</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>5.422902424536395</v>
+        <v>2.192229698691393</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02062139212879437</v>
+        <v>0.008333563627179606</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>5.394473106859761</v>
+        <v>2.180734450292196</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0136389554946352</v>
+        <v>0.005510641582937633</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>5.401120666069575</v>
+        <v>2.18341892269172</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.006978129468436481</v>
+        <v>0.002817967231921131</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>5.401429877737424</v>
+        <v>2.183540957973626</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003567643925846413</v>
+        <v>0.001439560167255453</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC52" t="n">
-        <v>5.40158189751869</v>
+        <v>2.183599447234295</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001337713843082617</v>
+        <v>0.0005376864856202011</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>5.400687731967579</v>
+        <v>2.183234922977324</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0007267803018283804</v>
+        <v>0.0002911771458358382</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>5.400802898942684</v>
+        <v>2.183278531161338</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0003478600980478978</v>
+        <v>0.0001372566611499408</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>5.400770550587687</v>
+        <v>2.183262475273386</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.000213438036070579</v>
+        <v>8.355596056915365e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>5.400849401560732</v>
+        <v>2.183291468911106</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001092599764808851</v>
+        <v>4.132161208684532e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>5.400854356563369</v>
+        <v>2.183290504722986</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>4.995012219318478e-05</v>
+        <v>1.698004887727391e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>5.400845925000115</v>
+        <v>2.183284113910244</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.081609857735592e-05</v>
+        <v>9.070610155389825e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>5.40085658335164</v>
+        <v>2.1832855457952</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.131855788691358e-05</v>
+        <v>1.993667665820105e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC60" t="n">
-        <v>5.400848380722908</v>
+        <v>2.18327917324003</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>2.205584102398162e-06</v>
+        <v>-1.911892527543644e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>5.400841462274134</v>
+        <v>2.183273351047698</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-1.662115307266386e-06</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC62" t="n">
-        <v>5.400837041730283</v>
+        <v>2.183268599772485</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>5.40083146343516</v>
+        <v>2.183263310624922</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.053889915940302e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>5.400826416814093</v>
+        <v>2.183263287890621</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>5.400826735094308</v>
+        <v>2.183263606170838</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>5.400827826340766</v>
+        <v>2.183264697417295</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>5.400827136733629</v>
+        <v>2.183264007810159</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>5.400827167046032</v>
+        <v>2.183264038122561</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC69" t="n">
-        <v>5.400826977593521</v>
+        <v>2.18326384867005</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC70" t="n">
-        <v>5.400827030640225</v>
+        <v>2.183263901716753</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC71" t="n">
-        <v>5.400827083686927</v>
+        <v>2.183263954763456</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC72" t="n">
-        <v>5.400827045796425</v>
+        <v>2.183263916872954</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>5.400826916968718</v>
+        <v>2.183263788045247</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>5.400826772984811</v>
+        <v>2.18326364406134</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>5.400826613844703</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>5.400826666891406</v>
+        <v>2.183263537967934</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC77" t="n">
-        <v>5.400826613844703</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>5.400826613844703</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC79" t="n">
-        <v>5.400826431970294</v>
+        <v>2.183263303046822</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>5.400826598688502</v>
+        <v>2.183263469765031</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>5.400826795719112</v>
+        <v>2.183263666795641</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>5.400826636579004</v>
+        <v>2.183263507655533</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>5.400826674469505</v>
+        <v>2.183263545546035</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>5.400826871500116</v>
+        <v>2.183263742576645</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>5.400826848765814</v>
+        <v>2.183263719842344</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>5.400826697203807</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>5.400826621422803</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>5.400826719938109</v>
+        <v>2.183263591014637</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>5.400826727516209</v>
+        <v>2.183263598592738</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>5.400826992749723</v>
+        <v>2.183263863826252</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>5.400826697203807</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>5.40082693970302</v>
+        <v>2.183263810779549</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>5.400827023062124</v>
+        <v>2.183263894138653</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>5.400826856343916</v>
+        <v>2.183263727420444</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>5.400827045796425</v>
+        <v>2.183263916872954</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>5.400826697203807</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>5.400826492595096</v>
+        <v>2.183263363671625</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>5.400826606266602</v>
+        <v>2.183263477343131</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>5.400826621422803</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>5.400826386501691</v>
+        <v>2.18326325757822</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>5.400826447126494</v>
+        <v>2.183263318203023</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.901262215535431</v>
+        <v>-0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>5.400826318298787</v>
+        <v>2.183263189375316</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>5.400826454704595</v>
+        <v>2.183263325781123</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>5.400826629000903</v>
+        <v>2.183263500077433</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>5.400826772984811</v>
+        <v>2.18326364406134</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC106" t="n">
-        <v>5.400826606266602</v>
+        <v>2.183263477343131</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>5.400826598688502</v>
+        <v>2.183263469765031</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC108" t="n">
-        <v>5.400826310720687</v>
+        <v>2.183263181797216</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC109" t="n">
-        <v>5.400826325876888</v>
+        <v>2.183263196953417</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>5.4008265532199</v>
+        <v>2.183263424296428</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC111" t="n">
-        <v>5.400826538063699</v>
+        <v>2.183263409140228</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>5.400826644157104</v>
+        <v>2.183263515233633</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.901262215535431</v>
+        <v>-0.3</v>
       </c>
       <c r="JC113" t="n">
-        <v>5.40082637134549</v>
+        <v>2.183263242422019</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>5.400826469860795</v>
+        <v>2.183263340937324</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC115" t="n">
-        <v>5.400826621422803</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>5.400826636579004</v>
+        <v>2.183263507655533</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>5.400826613844703</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>5.400826697203807</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>5.400826795719112</v>
+        <v>2.183263666795641</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>5.400826629000903</v>
+        <v>2.183263500077433</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>5.400826613844703</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>5.400826583532301</v>
+        <v>2.18326345460883</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>5.4008265683761</v>
+        <v>2.183263439452629</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>5.400826606266602</v>
+        <v>2.183263477343131</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC125" t="n">
-        <v>5.400826621422803</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
-        <v>5.400826613844703</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_3_000007.xlsx
+++ b/out/LSTM-mamba2_repeat_3_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.190398199542422</v>
+        <v>0.06389352766843717</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636434</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.6427717100636433</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.190398199542422</v>
+        <v>0.06389352766843724</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.190398199542422</v>
+        <v>0.06389352766843724</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.901262215535431</v>
+        <v>-0.6427717100636433</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636434</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.8427717100636433</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636433</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636433</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.190398199542422</v>
+        <v>0.06389352766843738</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001907775237525348</v>
+        <v>-0.000158761361365905</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.199383012872231</v>
+        <v>1.830284021049803</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC40" t="n">
-        <v>4.402166026517913</v>
+        <v>3.663397330887086</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3298073164246632</v>
+        <v>0.2744592307523955</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.859445620448554</v>
+        <v>2.379575323854928</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4123664578916351</v>
+        <v>0.3431633984395382</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.354423595509047</v>
+        <v>2.791486430647995</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.5911251991053647</v>
+        <v>0.4919231042444084</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.124540578076084</v>
+        <v>3.432362902991704</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.6323872211502458</v>
+        <v>0.5262602815187645</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC44" t="n">
-        <v>4.798233569177909</v>
+        <v>3.992997038687232</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.6702029908713697</v>
+        <v>0.557729087990752</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC45" t="n">
-        <v>5.506300182504891</v>
+        <v>4.58223623187147</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3024494789631552</v>
+        <v>0.2516934301952719</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC46" t="n">
-        <v>5.440440546272648</v>
+        <v>4.527429056895574</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1460699175820781</v>
+        <v>0.1215564227481489</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC47" t="n">
-        <v>5.42989240798476</v>
+        <v>4.518651110155049</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.06959796694958495</v>
+        <v>0.0579174035788675</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC48" t="n">
-        <v>5.422902424536395</v>
+        <v>4.512834188634268</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02062139212879437</v>
+        <v>0.01716088587279464</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC49" t="n">
-        <v>5.394473106859761</v>
+        <v>4.48917563672647</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0136389554946352</v>
+        <v>0.01134926252660497</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC50" t="n">
-        <v>5.401120666069575</v>
+        <v>4.494706820252497</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.006978129468436481</v>
+        <v>0.005806238923571349</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC51" t="n">
-        <v>5.401429877737424</v>
+        <v>4.494963305554296</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003567643925846413</v>
+        <v>0.002967673291920106</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC52" t="n">
-        <v>5.40158189751869</v>
+        <v>4.495088979011076</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001337713843082617</v>
+        <v>0.001112919022679271</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC53" t="n">
-        <v>5.400687731967579</v>
+        <v>4.494343884222575</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0007267803018283804</v>
+        <v>0.0006038544112168486</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC54" t="n">
-        <v>5.400802898942684</v>
+        <v>4.494438876770332</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0003478600980478978</v>
+        <v>0.0002882553517560232</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC55" t="n">
-        <v>5.400770550587687</v>
+        <v>4.494411117757493</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.000213438036070579</v>
+        <v>0.0001770316967254824</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC56" t="n">
-        <v>5.400849401560732</v>
+        <v>4.494475993568365</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001092599764808851</v>
+        <v>8.970196248866155e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC57" t="n">
-        <v>5.400854356563369</v>
+        <v>4.494479290030143</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>4.995012219318478e-05</v>
+        <v>4.095828401611818e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC58" t="n">
-        <v>5.400845925000115</v>
+        <v>4.494471415035211</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.081609857735592e-05</v>
+        <v>2.442036668854237e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC59" t="n">
-        <v>5.40085658335164</v>
+        <v>4.49447955764225</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.131855788691358e-05</v>
+        <v>8.987335331640211e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.1361064723315627</v>
       </c>
       <c r="JC60" t="n">
-        <v>5.400848380722908</v>
+        <v>4.494471812531908</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>2.205584102398162e-06</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.1361064723315627</v>
       </c>
       <c r="JC61" t="n">
-        <v>5.400841462274134</v>
+        <v>4.494465168147245</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.1361064723315627</v>
       </c>
       <c r="JC62" t="n">
-        <v>5.400837041730283</v>
+        <v>4.49446066424429</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC63" t="n">
-        <v>5.40083146343516</v>
+        <v>4.494455231112821</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.190398199542422</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC64" t="n">
-        <v>5.400826416814093</v>
+        <v>4.494450184491754</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC65" t="n">
-        <v>5.400826735094308</v>
+        <v>4.494450502771969</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC66" t="n">
-        <v>5.400827826340766</v>
+        <v>4.494451594018427</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC67" t="n">
-        <v>5.400827136733629</v>
+        <v>4.49445090441129</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC68" t="n">
-        <v>5.400827167046032</v>
+        <v>4.494450934723693</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC69" t="n">
-        <v>5.400826977593521</v>
+        <v>4.494450745271183</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC70" t="n">
-        <v>5.400827030640225</v>
+        <v>4.494450798317886</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC71" t="n">
-        <v>5.400827083686927</v>
+        <v>4.494450851364588</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC72" t="n">
-        <v>5.400827045796425</v>
+        <v>4.494450813474086</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC73" t="n">
-        <v>5.400826916968718</v>
+        <v>4.494450684646379</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC74" t="n">
-        <v>5.400826772984811</v>
+        <v>4.494450540662472</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC75" t="n">
-        <v>5.400826613844703</v>
+        <v>4.494450381522364</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC76" t="n">
-        <v>5.400826666891406</v>
+        <v>4.494450434569067</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC77" t="n">
-        <v>5.400826613844703</v>
+        <v>4.494450381522364</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC78" t="n">
-        <v>5.400826613844703</v>
+        <v>4.494450381522364</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC79" t="n">
-        <v>5.400826431970294</v>
+        <v>4.494450199647955</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC80" t="n">
-        <v>5.400826598688502</v>
+        <v>4.494450366366163</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC81" t="n">
-        <v>5.400826795719112</v>
+        <v>4.494450563396773</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC82" t="n">
-        <v>5.400826636579004</v>
+        <v>4.494450404256665</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC83" t="n">
-        <v>5.400826674469505</v>
+        <v>4.494450442147166</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC84" t="n">
-        <v>5.400826871500116</v>
+        <v>4.494450639177777</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC85" t="n">
-        <v>5.400826848765814</v>
+        <v>4.494450616443475</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.1361064723315627</v>
       </c>
       <c r="JC86" t="n">
-        <v>5.400826697203807</v>
+        <v>4.494450464881468</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.1361064723315627</v>
       </c>
       <c r="JC87" t="n">
-        <v>5.400826621422803</v>
+        <v>4.494450389100464</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.1361064723315627</v>
       </c>
       <c r="JC88" t="n">
-        <v>5.400826719938109</v>
+        <v>4.49445048761577</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC89" t="n">
-        <v>5.400826727516209</v>
+        <v>4.49445049519387</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.190398199542422</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC90" t="n">
-        <v>5.400826992749723</v>
+        <v>4.494450760427384</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC91" t="n">
-        <v>5.400826697203807</v>
+        <v>4.494450464881468</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC92" t="n">
-        <v>5.40082693970302</v>
+        <v>4.494450707380681</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC93" t="n">
-        <v>5.400827023062124</v>
+        <v>4.494450790739785</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC94" t="n">
-        <v>5.400826856343916</v>
+        <v>4.494450624021577</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC95" t="n">
-        <v>5.400827045796425</v>
+        <v>4.494450813474086</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.1361064723315627</v>
       </c>
       <c r="JC96" t="n">
-        <v>5.400826697203807</v>
+        <v>4.494450464881468</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636433</v>
       </c>
       <c r="JC97" t="n">
-        <v>5.400826492595096</v>
+        <v>4.494450260272757</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC98" t="n">
-        <v>5.400826606266602</v>
+        <v>4.494450373944263</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636433</v>
       </c>
       <c r="JC99" t="n">
-        <v>5.400826621422803</v>
+        <v>4.494450389100464</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.1361064723315626</v>
       </c>
       <c r="JC100" t="n">
-        <v>5.400826386501691</v>
+        <v>4.494450154179352</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.1361064723315626</v>
       </c>
       <c r="JC101" t="n">
-        <v>5.400826447126494</v>
+        <v>4.494450214804155</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.901262215535431</v>
+        <v>0.06389352766843738</v>
       </c>
       <c r="JC102" t="n">
-        <v>5.400826318298787</v>
+        <v>4.494450085976448</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.190398199542422</v>
+        <v>0.06389352766843738</v>
       </c>
       <c r="JC103" t="n">
-        <v>5.400826454704595</v>
+        <v>4.494450222382256</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC104" t="n">
-        <v>5.400826629000903</v>
+        <v>4.494450396678564</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC105" t="n">
-        <v>5.400826772984811</v>
+        <v>4.494450540662472</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC106" t="n">
-        <v>5.400826606266602</v>
+        <v>4.494450373944263</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.190398199542422</v>
+        <v>0.06389352766843731</v>
       </c>
       <c r="JC107" t="n">
-        <v>5.400826598688502</v>
+        <v>4.494450366366163</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636433</v>
       </c>
       <c r="JC108" t="n">
-        <v>5.400826310720687</v>
+        <v>4.494450078398348</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC109" t="n">
-        <v>5.400826325876888</v>
+        <v>4.494450093554549</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636433</v>
       </c>
       <c r="JC110" t="n">
-        <v>5.4008265532199</v>
+        <v>4.494450320897561</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.1361064723315626</v>
       </c>
       <c r="JC111" t="n">
-        <v>5.400826538063699</v>
+        <v>4.49445030574136</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.1361064723315626</v>
       </c>
       <c r="JC112" t="n">
-        <v>5.400826644157104</v>
+        <v>4.494450411834765</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.901262215535431</v>
+        <v>0.06389352766843738</v>
       </c>
       <c r="JC113" t="n">
-        <v>5.40082637134549</v>
+        <v>4.494450139023151</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.190398199542422</v>
+        <v>0.06389352766843738</v>
       </c>
       <c r="JC114" t="n">
-        <v>5.400826469860795</v>
+        <v>4.494450237538456</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC115" t="n">
-        <v>5.400826621422803</v>
+        <v>4.494450389100464</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC116" t="n">
-        <v>5.400826636579004</v>
+        <v>4.494450404256665</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC117" t="n">
-        <v>5.400826613844703</v>
+        <v>4.494450381522364</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC118" t="n">
-        <v>5.400826697203807</v>
+        <v>4.494450464881468</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.190398199542422</v>
+        <v>0.06389352766843738</v>
       </c>
       <c r="JC119" t="n">
-        <v>5.400826795719112</v>
+        <v>4.494450563396773</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636433</v>
       </c>
       <c r="JC120" t="n">
-        <v>5.400826629000903</v>
+        <v>4.494450396678564</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636433</v>
       </c>
       <c r="JC121" t="n">
-        <v>5.400826613844703</v>
+        <v>4.494450381522364</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.5903981995424217</v>
+        <v>-0.1361064723315626</v>
       </c>
       <c r="JC122" t="n">
-        <v>5.400826583532301</v>
+        <v>4.494450351209962</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.5903981995424217</v>
+        <v>0.5705587654005178</v>
       </c>
       <c r="JC123" t="n">
-        <v>5.4008265683761</v>
+        <v>4.494450336053761</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC124" t="n">
-        <v>5.400826606266602</v>
+        <v>4.494450373944263</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC125" t="n">
-        <v>5.400826621422803</v>
+        <v>4.494450389100464</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005178</v>
       </c>
       <c r="JC126" t="n">
-        <v>5.400826613844703</v>
+        <v>4.494450381522364</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_3_000007.xlsx
+++ b/out/LSTM-mamba2_repeat_3_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.2520003318786621</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.1472562402486801</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.04021593183279037</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.7705587654005178</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.02879178524017334</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.7705587654005178</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.001576736569404602</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.06389352766843717</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.01888158172369003</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8427717100636434</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.03142703324556351</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.02699110470712185</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.02162106893956661</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.01549739018082619</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.01480823010206223</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.01744166761636734</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.01113846898078918</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.008063733577728271</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.001160651445388794</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.00851484015583992</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.01286504417657852</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.01745990291237831</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.01232641562819481</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.00922059640288353</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6427717100636433</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.001961909234523773</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.06389352766843724</v>
+        <v>0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.02577501535415649</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.01964052766561508</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.004465654492378235</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.06389352766843724</v>
+        <v>0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.007099777460098267</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6427717100636433</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.01256865635514259</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.01741324365139008</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.005269706249237061</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.8427717100636434</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.003206834197044373</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.8427717100636433</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.0007436275482177734</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.8427717100636433</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.006366804242134094</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.01029504090547562</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.01100926101207733</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.009229488670825958</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.8427717100636433</v>
+        <v>0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.01456803828477859</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.06389352766843738</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0835641473531723</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.07290537655353546</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.05094565451145172</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.000158761361365905</v>
+        <v>-0.0001762581139509566</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.830284021049803</v>
+        <v>2.031995661651695</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.03771638125181198</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>3.663397330887086</v>
+        <v>4.067132573440041</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.2744592307523955</v>
+        <v>0.304706836431729</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.02590145915746689</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.379575323854928</v>
+        <v>2.641823215454815</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.3431633984395382</v>
+        <v>0.3809826339917982</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01400961726903915</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.791486430647995</v>
+        <v>3.099130150153705</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.4919231042444084</v>
+        <v>0.5461367990545677</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.04066959768533707</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>3.432362902991704</v>
+        <v>3.810636331820818</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.5262602815187645</v>
+        <v>0.5842581963286199</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.06619689613580704</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>3.992997038687232</v>
+        <v>4.43305701572845</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.557729087990752</v>
+        <v>0.619196663161341</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.07699151337146759</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>4.58223623187147</v>
+        <v>5.087235660467096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2516934301952719</v>
+        <v>0.2794319377854967</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.06295455992221832</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.5705587654005178</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>4.527429056895574</v>
+        <v>5.026388322909726</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1215564227481489</v>
+        <v>0.1349522109205024</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.02980230748653412</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC47" t="n">
-        <v>4.518651110155049</v>
+        <v>5.016642981444461</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0579174035788675</v>
+        <v>0.06430132361609035</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.03033077716827393</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>4.512834188634268</v>
+        <v>5.010184959644628</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01716088587279464</v>
+        <v>0.01905167046229239</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.0163201242685318</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>4.48917563672647</v>
+        <v>4.983919210836554</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01134926252660497</v>
+        <v>0.01260080754943257</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.01520518958568573</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>4.494706820252497</v>
+        <v>4.990060604748933</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.005806238923571349</v>
+        <v>0.00644679370502156</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.009070076048374176</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>4.494963305554296</v>
+        <v>4.990345910255853</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002967673291920106</v>
+        <v>0.003295845148732146</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.01962687075138092</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>4.495088979011076</v>
+        <v>4.990485984322567</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001112919022679271</v>
+        <v>0.001235534379262914</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.02446603029966354</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>4.494343884222575</v>
+        <v>4.9896594645375</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0006038544112168486</v>
+        <v>0.0006715049013520539</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.020405612885952</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>4.494438876770332</v>
+        <v>4.989765491587336</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002882553517560232</v>
+        <v>0.0003208392797289147</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.01718315482139587</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>4.494411117757493</v>
+        <v>4.98973523747574</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001770316967254824</v>
+        <v>0.0001967107990741833</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.02301778644323349</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.5705587654005178</v>
+        <v>0.16</v>
       </c>
       <c r="JC56" t="n">
-        <v>4.494475993568365</v>
+        <v>4.989807667428328</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>8.970196248866155e-05</v>
+        <v>9.999565406351607e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.00628335028886795</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.5705587654005178</v>
+        <v>0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>4.494479290030143</v>
+        <v>4.98981186073719</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>4.095828401611818e-05</v>
+        <v>4.595374967004406e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.06535328924655914</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.5705587654005178</v>
+        <v>0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>4.494471415035211</v>
+        <v>4.989803676537635</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.442036668854237e-05</v>
+        <v>2.82578058218305e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.05507130920886993</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.5705587654005178</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>4.49447955764225</v>
+        <v>4.989813216435479</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>8.987335331640211e-06</v>
+        <v>1.015294660927689e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.01748364418745041</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1361064723315627</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>4.494471812531908</v>
+        <v>4.989805242565942</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0007846467196941376</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1361064723315627</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>4.494465168147245</v>
+        <v>4.989798461775472</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.003559429198503494</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.1361064723315627</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>4.49446066424429</v>
+        <v>4.989794041231621</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.0126899778842926</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>4.494455231112821</v>
+        <v>4.989788462936497</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.03131159394979477</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>4.494450184491754</v>
+        <v>4.98978341631543</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.06108924001455307</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.7705587654005178</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>4.494450502771969</v>
+        <v>4.989783734595646</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01791293919086456</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.7705587654005178</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>4.494451594018427</v>
+        <v>4.989784825842103</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.002151928842067719</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.7705587654005178</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>4.49445090441129</v>
+        <v>4.989784136234967</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.01057753711938858</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.7705587654005178</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>4.494450934723693</v>
+        <v>4.989784166547369</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.01560597121715546</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.7705587654005178</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>4.494450745271183</v>
+        <v>4.989783977094859</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.01600038260221481</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.7705587654005178</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>4.494450798317886</v>
+        <v>4.989784030141562</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.01075771450996399</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.7705587654005178</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>4.494450851364588</v>
+        <v>4.989784083188264</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.007691431790590286</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>4.494450813474086</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.01571944355964661</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>4.494450684646379</v>
+        <v>4.989783916470055</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.02231159806251526</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.5705587654005178</v>
+        <v>0.16</v>
       </c>
       <c r="JC74" t="n">
-        <v>4.494450540662472</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.02241532504558563</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.5705587654005178</v>
+        <v>0.16</v>
       </c>
       <c r="JC75" t="n">
-        <v>4.494450381522364</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.02242834866046906</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.5705587654005178</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC76" t="n">
-        <v>4.494450434569067</v>
+        <v>4.989783666392743</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.007109027355909348</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.5705587654005178</v>
+        <v>0.16</v>
       </c>
       <c r="JC77" t="n">
-        <v>4.494450381522364</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.01072055846452713</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.5705587654005178</v>
+        <v>0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>4.494450381522364</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.02165191620588303</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.5705587654005178</v>
+        <v>0.16</v>
       </c>
       <c r="JC79" t="n">
-        <v>4.494450199647955</v>
+        <v>4.989783431471631</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.02797108143568039</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.5705587654005178</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>4.494450366366163</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.0194268673658371</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.5705587654005178</v>
+        <v>0.16</v>
       </c>
       <c r="JC81" t="n">
-        <v>4.494450563396773</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.001941386610269547</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.5705587654005178</v>
+        <v>0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>4.494450404256665</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.01303645223379135</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.5705587654005178</v>
+        <v>0.16</v>
       </c>
       <c r="JC83" t="n">
-        <v>4.494450442147166</v>
+        <v>4.989783673970843</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.03064532577991486</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>4.494450639177777</v>
+        <v>4.989783871001453</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.01992091536521912</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>4.494450616443475</v>
+        <v>4.989783848267152</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.002266939729452133</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1361064723315627</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>4.494450464881468</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.002819560468196869</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1361064723315627</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>4.494450389100464</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.002748690545558929</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1361064723315627</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>4.49445048761577</v>
+        <v>4.989783719439446</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.02197513729333878</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>4.49445049519387</v>
+        <v>4.989783727017546</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.02362252771854401</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>4.494450760427384</v>
+        <v>4.98978399225106</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.01033489033579826</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.16</v>
       </c>
       <c r="JC91" t="n">
-        <v>4.494450464881468</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.01815950125455856</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>4.494450707380681</v>
+        <v>4.989783939204357</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.01084549725055695</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>4.494450790739785</v>
+        <v>4.989784022563462</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.03653708100318909</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>4.494450624021577</v>
+        <v>4.989783855845253</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.02785816788673401</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>4.494450813474086</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.008254930377006531</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1361064723315627</v>
+        <v>0.16</v>
       </c>
       <c r="JC96" t="n">
-        <v>4.494450464881468</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01200834661722183</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8427717100636433</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>4.494450260272757</v>
+        <v>4.989783492096433</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.01641755551099777</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>4.494450373944263</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-4.284083843231201e-05</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8427717100636433</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>4.494450389100464</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.007935747504234314</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.1361064723315626</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>4.494450154179352</v>
+        <v>4.989783386003029</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.003853131085634232</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.1361064723315626</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>4.494450214804155</v>
+        <v>4.989783446627831</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.003128070384263992</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.06389352766843738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>4.494450085976448</v>
+        <v>4.989783317800124</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.02902400493621826</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.06389352766843738</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>4.494450222382256</v>
+        <v>4.989783454205933</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.01911020278930664</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC104" t="n">
-        <v>4.494450396678564</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.006995540112257004</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>4.494450540662472</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.007030192762613297</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC106" t="n">
-        <v>4.494450373944263</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.01072989404201508</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.06389352766843731</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>4.494450366366163</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.001046013087034225</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8427717100636433</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>4.494450078398348</v>
+        <v>4.989783310222024</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.005431648343801498</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>4.494450093554549</v>
+        <v>4.989783325378225</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.002393715083599091</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8427717100636433</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>4.494450320897561</v>
+        <v>4.989783552721237</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.01069588214159012</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.1361064723315626</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>4.49445030574136</v>
+        <v>4.989783537565036</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.005194120109081268</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.1361064723315626</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>4.494450411834765</v>
+        <v>4.989783643658441</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.001144677400588989</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.06389352766843738</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>4.494450139023151</v>
+        <v>4.989783370846827</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.001159362494945526</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.06389352766843738</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>4.494450237538456</v>
+        <v>4.989783469362132</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.004399463534355164</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7705587654005178</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>4.494450389100464</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.003887880593538284</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC116" t="n">
-        <v>4.494450404256665</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.006563097238540649</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC117" t="n">
-        <v>4.494450381522364</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.01303484290838242</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC118" t="n">
-        <v>4.494450464881468</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.003630846738815308</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.06389352766843738</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC119" t="n">
-        <v>4.494450563396773</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.003534026443958282</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8427717100636433</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>4.494450396678564</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003015853464603424</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8427717100636433</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>4.494450381522364</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.001968637108802795</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.1361064723315626</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>4.494450351209962</v>
+        <v>4.989783583033638</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.003847941756248474</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.5705587654005178</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>4.494450336053761</v>
+        <v>4.989783567877438</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.0004601962864398956</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>4.494450373944263</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.005317755043506622</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7705587654005178</v>
+        <v>0.6500000000000004</v>
       </c>
       <c r="JC125" t="n">
-        <v>4.494450389100464</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
+        <v>0.01697994768619537</v>
+      </c>
+      <c r="JB126" t="n">
         <v>1</v>
       </c>
-      <c r="JB126" t="n">
-        <v>0.7705587654005178</v>
-      </c>
       <c r="JC126" t="n">
-        <v>4.494450381522364</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
   </sheetData>
